--- a/114_teacher_record.xlsx
+++ b/114_teacher_record.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\study_system\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\nginxphp\nginx-1.26.3\html\teacher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F41C29E-70B0-41D6-8790-0E44F459C53C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B87C3F-CDFE-485F-A484-3D5110E85525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="研習紀錄" sheetId="1" r:id="rId1"/>
     <sheet name="教師名稱" sheetId="2" r:id="rId2"/>
+    <sheet name="段考命題" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="42">
   <si>
     <t>職碼</t>
   </si>
@@ -271,12 +272,29 @@
     <t>0.5日</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>姓名</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>114出題次數</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>115出題次數</t>
+  </si>
+  <si>
+    <t>116出題次數</t>
+  </si>
+  <si>
+    <t>117出題次數</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -339,6 +357,13 @@
       <family val="2"/>
       <charset val="136"/>
     </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -386,7 +411,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -406,6 +431,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1103,4 +1129,100 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4C57A7-E254-45F6-BA12-A6B669FB8A10}">
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.875" customWidth="1"/>
+    <col min="2" max="2" width="20.25" customWidth="1"/>
+    <col min="3" max="3" width="23.625" customWidth="1"/>
+    <col min="4" max="4" width="23.75" customWidth="1"/>
+    <col min="5" max="5" width="15.5" customWidth="1"/>
+    <col min="6" max="6" width="20.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="7" customFormat="1" ht="24.6" x14ac:dyDescent="0.45">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/114_teacher_record.xlsx
+++ b/114_teacher_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\nginxphp\nginx-1.26.3\html\teacher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B87C3F-CDFE-485F-A484-3D5110E85525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45ACFAF-64EA-405C-9B0B-059E77111EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1140,8 +1140,8 @@
     <col min="2" max="2" width="20.25" customWidth="1"/>
     <col min="3" max="3" width="23.625" customWidth="1"/>
     <col min="4" max="4" width="23.75" customWidth="1"/>
-    <col min="5" max="5" width="15.5" customWidth="1"/>
-    <col min="6" max="6" width="20.125" customWidth="1"/>
+    <col min="5" max="5" width="28" customWidth="1"/>
+    <col min="6" max="6" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="7" customFormat="1" ht="24.6" x14ac:dyDescent="0.45">
@@ -1174,6 +1174,9 @@
       <c r="C2" s="2">
         <v>4</v>
       </c>
+      <c r="D2" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="3" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2">
@@ -1185,6 +1188,9 @@
       <c r="C3" s="2">
         <v>3</v>
       </c>
+      <c r="D3" s="2">
+        <v>4</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2">
@@ -1196,6 +1202,9 @@
       <c r="C4" s="2">
         <v>3</v>
       </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2">
@@ -1207,6 +1216,9 @@
       <c r="C5" s="2">
         <v>4</v>
       </c>
+      <c r="D5" s="2">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2">
@@ -1217,6 +1229,9 @@
       </c>
       <c r="C6" s="2">
         <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/114_teacher_record.xlsx
+++ b/114_teacher_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\nginxphp\nginx-1.26.3\html\teacher\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E45ACFAF-64EA-405C-9B0B-059E77111EFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B9C5DD-A1EC-46AD-BEF1-F08D79FF6CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="75">
   <si>
     <t>職碼</t>
   </si>
@@ -288,6 +288,105 @@
   </si>
   <si>
     <t>117出題次數</t>
+  </si>
+  <si>
+    <t>118出題次數</t>
+  </si>
+  <si>
+    <t>119出題次數</t>
+  </si>
+  <si>
+    <t>120出題次數</t>
+  </si>
+  <si>
+    <t>121出題次數</t>
+  </si>
+  <si>
+    <t>122出題次數</t>
+  </si>
+  <si>
+    <t>123出題次數</t>
+  </si>
+  <si>
+    <t>124出題次數</t>
+  </si>
+  <si>
+    <t>125出題次數</t>
+  </si>
+  <si>
+    <t>126出題次數</t>
+  </si>
+  <si>
+    <t>127出題次數</t>
+  </si>
+  <si>
+    <t>128出題次數</t>
+  </si>
+  <si>
+    <t>129出題次數</t>
+  </si>
+  <si>
+    <t>130出題次數</t>
+  </si>
+  <si>
+    <t>131出題次數</t>
+  </si>
+  <si>
+    <t>132出題次數</t>
+  </si>
+  <si>
+    <t>133出題次數</t>
+  </si>
+  <si>
+    <t>134出題次數</t>
+  </si>
+  <si>
+    <t>135出題次數</t>
+  </si>
+  <si>
+    <t>136出題次數</t>
+  </si>
+  <si>
+    <t>137出題次數</t>
+  </si>
+  <si>
+    <t>138出題次數</t>
+  </si>
+  <si>
+    <t>139出題次數</t>
+  </si>
+  <si>
+    <t>140出題次數</t>
+  </si>
+  <si>
+    <t>141出題次數</t>
+  </si>
+  <si>
+    <t>142出題次數</t>
+  </si>
+  <si>
+    <t>143出題次數</t>
+  </si>
+  <si>
+    <t>144出題次數</t>
+  </si>
+  <si>
+    <t>145出題次數</t>
+  </si>
+  <si>
+    <t>146出題次數</t>
+  </si>
+  <si>
+    <t>147出題次數</t>
+  </si>
+  <si>
+    <t>148出題次數</t>
+  </si>
+  <si>
+    <t>149出題次數</t>
+  </si>
+  <si>
+    <t>150出題次數</t>
   </si>
 </sst>
 </file>
@@ -1133,7 +1232,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C4C57A7-E254-45F6-BA12-A6B669FB8A10}">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:AM8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.875" customWidth="1"/>
@@ -1144,7 +1243,7 @@
     <col min="6" max="6" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" ht="24.6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:39" s="7" customFormat="1" ht="24.6" x14ac:dyDescent="0.45">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1163,8 +1262,107 @@
       <c r="F1" s="7" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="G1" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="M1" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="N1" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q1" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="R1" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="S1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="V1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="W1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="X1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="Y1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="AB1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="AC1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="AD1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="AF1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="AG1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="AH1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="AI1" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="AJ1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="AK1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="AL1" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AM1" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:39" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1178,7 +1376,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:39" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -1192,7 +1390,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:39" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -1206,7 +1404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:39" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -1220,7 +1418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="24.6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:39" ht="24.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -1234,8 +1432,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="32.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="8" spans="1:6" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="7" spans="1:39" ht="32.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:39" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
